--- a/data/trans_orig/P16A03-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A03-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13162</t>
+          <t>13160</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10949</t>
+          <t>10581</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27999</t>
+          <t>27232</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15633</t>
+          <t>16040</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36408</t>
+          <t>35692</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>259848</t>
+          <t>259850</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>232839</t>
+          <t>233606</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>249889</t>
+          <t>250257</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>497440</t>
+          <t>498156</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>518215</t>
+          <t>517808</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20510</t>
+          <t>19724</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13845</t>
+          <t>13563</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31024</t>
+          <t>31710</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19913</t>
+          <t>20536</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43937</t>
+          <t>45538</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>472565</t>
+          <t>473351</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>489392</t>
+          <t>489229</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>472925</t>
+          <t>472239</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>490104</t>
+          <t>490386</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>953087</t>
+          <t>951486</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>977111</t>
+          <t>976488</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11263</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11090</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28326</t>
+          <t>26185</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14286</t>
+          <t>14124</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31984</t>
+          <t>33240</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307583</t>
+          <t>307119</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317900</t>
+          <t>317896</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>307086</t>
+          <t>309227</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>324322</t>
+          <t>324626</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>622274</t>
+          <t>621018</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>639972</t>
+          <t>640134</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17464</t>
+          <t>17551</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34946</t>
+          <t>37097</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27656</t>
+          <t>25865</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49846</t>
+          <t>50440</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>352680</t>
+          <t>352414</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>336510</t>
+          <t>334359</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>353992</t>
+          <t>353905</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>680281</t>
+          <t>679687</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>702471</t>
+          <t>704262</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>5477</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19537</t>
+          <t>19298</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19542</t>
+          <t>19762</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199058</t>
+          <t>197831</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188131</t>
+          <t>188370</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>202149</t>
+          <t>202072</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>391434</t>
+          <t>391214</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>404838</t>
+          <t>405076</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10837</t>
+          <t>11868</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>11434</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28042</t>
+          <t>27451</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,47 +2498,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>22916</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>14848</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>33973</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
           <t>4,17%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>10,08%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>22916</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>14966</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>33948</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259974</t>
+          <t>258943</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268914</t>
+          <t>268966</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>250102</t>
+          <t>250693</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>266549</t>
+          <t>266710</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,47 +2611,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>95,89%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>526039</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>514982</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>534107</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>95,83%</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>526039</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>515007</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>533989</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>95,83%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10963</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29643</t>
+          <t>29193</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28978</t>
+          <t>30087</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55591</t>
+          <t>55205</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46262</t>
+          <t>46097</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75790</t>
+          <t>76712</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>585384</t>
+          <t>585834</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>604064</t>
+          <t>603752</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>582628</t>
+          <t>583014</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>609241</t>
+          <t>608132</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1177456</t>
+          <t>1176534</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1206984</t>
+          <t>1207149</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>11076</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29253</t>
+          <t>28730</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,82 +3149,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>26266</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>17741</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>37310</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>44646</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>33384</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>60069</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>3,94%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>26266</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>17584</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>37287</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>44646</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>32635</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>59478</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>713524</t>
+          <t>714047</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>731872</t>
+          <t>731701</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,82 +3262,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>96,13%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>757245</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>746201</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>765770</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>96,65%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>95,24%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>97,74%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1481642</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1466219</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>1492904</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>97,07%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>96,06%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>98,53%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>757245</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>746224</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>765927</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>96,65%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>95,24%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1436</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1481642</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1466810</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1493653</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>97,07%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>96,1%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>58615</t>
+          <t>57390</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>94985</t>
+          <t>91669</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>154147</t>
+          <t>154672</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>204663</t>
+          <t>206254</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>220429</t>
+          <t>222735</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>281987</t>
+          <t>286084</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3180540</t>
+          <t>3183856</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3216910</t>
+          <t>3218135</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3174534</t>
+          <t>3172943</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3225050</t>
+          <t>3224525</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6372735</t>
+          <t>6368638</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6434293</t>
+          <t>6431987</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13868</t>
+          <t>14714</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9978</t>
+          <t>9247</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27359</t>
+          <t>26380</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14357</t>
+          <t>14464</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36212</t>
+          <t>35613</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276335</t>
+          <t>275489</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288324</t>
+          <t>287551</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>252949</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>269351</t>
+          <t>270082</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>533320</t>
+          <t>533919</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>555175</t>
+          <t>555068</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23526</t>
+          <t>20094</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20442</t>
+          <t>19873</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43672</t>
+          <t>42371</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26132</t>
+          <t>25936</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53493</t>
+          <t>54049</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>482001</t>
+          <t>485433</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502422</t>
+          <t>502376</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>479059</t>
+          <t>480360</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502289</t>
+          <t>502858</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>974765</t>
+          <t>974209</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1002126</t>
+          <t>1002322</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10446</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12291</t>
+          <t>12246</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29661</t>
+          <t>29834</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15323</t>
+          <t>16157</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35007</t>
+          <t>36018</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312670</t>
+          <t>312541</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>321247</t>
+          <t>321222</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>310294</t>
+          <t>310121</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327664</t>
+          <t>327709</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>628064</t>
+          <t>627053</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>647748</t>
+          <t>646914</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11772</t>
+          <t>12593</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23047</t>
+          <t>23173</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45854</t>
+          <t>45398</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27658</t>
+          <t>27248</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52560</t>
+          <t>51201</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>362210</t>
+          <t>361389</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>372127</t>
+          <t>371930</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>342120</t>
+          <t>342576</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>364927</t>
+          <t>364801</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>709396</t>
+          <t>710755</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>734298</t>
+          <t>734708</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9627</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13477</t>
+          <t>13295</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32362</t>
+          <t>31243</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16061</t>
+          <t>16413</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36145</t>
+          <t>37534</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>202991</t>
+          <t>201260</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211567</t>
+          <t>211576</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>187229</t>
+          <t>188348</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206114</t>
+          <t>206296</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>396064</t>
+          <t>394675</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>416148</t>
+          <t>415796</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7044</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23095</t>
+          <t>23335</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>9637</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25343</t>
+          <t>25457</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>266937</t>
+          <t>267924</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>256045</t>
+          <t>255805</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>270951</t>
+          <t>271270</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>527778</t>
+          <t>527664</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>543271</t>
+          <t>543484</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3882</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>16792</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33053</t>
+          <t>33502</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60476</t>
+          <t>61044</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41257</t>
+          <t>39945</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71050</t>
+          <t>69386</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>645712</t>
+          <t>645996</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>659588</t>
+          <t>658906</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>633377</t>
+          <t>632809</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>660800</t>
+          <t>660351</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1285591</t>
+          <t>1287255</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1315384</t>
+          <t>1316696</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12435</t>
+          <t>14271</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24578</t>
+          <t>25978</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49419</t>
+          <t>49695</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28806</t>
+          <t>29687</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>54729</t>
+          <t>55725</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>764537</t>
+          <t>762701</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>774905</t>
+          <t>774841</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>772101</t>
+          <t>771825</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>796942</t>
+          <t>795542</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1543763</t>
+          <t>1542767</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1569686</t>
+          <t>1568805</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>34073</t>
+          <t>32689</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>61591</t>
+          <t>62370</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>185300</t>
+          <t>185266</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>243332</t>
+          <t>243139</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>227342</t>
+          <t>228931</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>292577</t>
+          <t>294050</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3357597</t>
+          <t>3356818</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3385115</t>
+          <t>3386499</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3300762</t>
+          <t>3300955</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3358794</t>
+          <t>3358828</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6670705</t>
+          <t>6669232</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6735940</t>
+          <t>6734351</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>802</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>9661</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12569</t>
+          <t>12709</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31026</t>
+          <t>31380</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15395</t>
+          <t>15230</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36867</t>
+          <t>34787</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>285595</t>
+          <t>284100</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292960</t>
+          <t>292959</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>257677</t>
+          <t>257323</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>276134</t>
+          <t>275994</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>545597</t>
+          <t>547677</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>567069</t>
+          <t>567234</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12586</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20798</t>
+          <t>19685</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10274</t>
+          <t>10358</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27976</t>
+          <t>27315</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>489989</t>
+          <t>489932</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500320</t>
+          <t>500390</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>502286</t>
+          <t>503399</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>516714</t>
+          <t>516882</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>997683</t>
+          <t>998344</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1015385</t>
+          <t>1015301</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>5889</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20345</t>
+          <t>20560</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22611</t>
+          <t>22559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313742</t>
+          <t>313753</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>315964</t>
+          <t>315749</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>329876</t>
+          <t>330420</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>632263</t>
+          <t>632315</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>647270</t>
+          <t>647689</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11811</t>
+          <t>11839</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20760</t>
+          <t>21111</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41630</t>
+          <t>42379</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24948</t>
+          <t>25028</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49258</t>
+          <t>49476</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>358153</t>
+          <t>358125</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368023</t>
+          <t>367963</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>345653</t>
+          <t>344904</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366523</t>
+          <t>366172</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>707989</t>
+          <t>707771</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>732299</t>
+          <t>732219</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14953</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>15062</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>207215</t>
+          <t>205891</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>203634</t>
+          <t>205310</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215527</t>
+          <t>215551</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>414928</t>
+          <t>414746</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>426091</t>
+          <t>426167</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>790</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17705</t>
+          <t>18585</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>7366</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21321</t>
+          <t>21709</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255161</t>
+          <t>254816</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262334</t>
+          <t>262333</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>255410</t>
+          <t>254530</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>268192</t>
+          <t>267776</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>514917</t>
+          <t>514529</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>529037</t>
+          <t>528872</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>9155</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25681</t>
+          <t>26200</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17012</t>
+          <t>17670</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36725</t>
+          <t>37897</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30289</t>
+          <t>31332</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55991</t>
+          <t>57259</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>630877</t>
+          <t>630358</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>646910</t>
+          <t>647403</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>654569</t>
+          <t>653397</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>674282</t>
+          <t>673624</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1291861</t>
+          <t>1290593</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1317563</t>
+          <t>1316520</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13394</t>
+          <t>13839</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20258</t>
+          <t>19336</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42611</t>
+          <t>42436</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25592</t>
+          <t>25764</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51637</t>
+          <t>51203</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>765189</t>
+          <t>764744</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775828</t>
+          <t>775609</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>783556</t>
+          <t>783731</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>805909</t>
+          <t>806831</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1553113</t>
+          <t>1553547</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1579158</t>
+          <t>1578986</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31640</t>
+          <t>32914</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>58547</t>
+          <t>58279</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>123591</t>
+          <t>122626</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>172901</t>
+          <t>175335</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>162858</t>
+          <t>166431</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>218963</t>
+          <t>217995</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3335803</t>
+          <t>3336071</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3362710</t>
+          <t>3361436</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3371641</t>
+          <t>3369207</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3420951</t>
+          <t>3421916</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6719929</t>
+          <t>6720897</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6776034</t>
+          <t>6772461</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17191</t>
+          <t>16655</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31358</t>
+          <t>31519</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20643</t>
+          <t>20713</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37571</t>
+          <t>37123</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>301096</t>
+          <t>301884</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309202</t>
+          <t>309586</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>258277</t>
+          <t>258116</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>272444</t>
+          <t>272980</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>563506</t>
+          <t>563954</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>580434</t>
+          <t>580364</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12995</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>19682</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11720</t>
+          <t>12207</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27934</t>
+          <t>28116</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>504398</t>
+          <t>505048</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>515364</t>
+          <t>515292</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>493783</t>
+          <t>494043</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>505824</t>
+          <t>505561</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1003184</t>
+          <t>1003002</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1019398</t>
+          <t>1018911</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21975</t>
+          <t>21865</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20344</t>
+          <t>20298</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36013</t>
+          <t>35278</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32160</t>
+          <t>30830</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51490</t>
+          <t>51715</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>293585</t>
+          <t>293695</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>307560</t>
+          <t>307457</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>313115</t>
+          <t>313850</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328784</t>
+          <t>328830</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>613198</t>
+          <t>612973</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>632528</t>
+          <t>633858</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>12337</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>4809</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17160</t>
+          <t>17319</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>7353</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22816</t>
+          <t>22116</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>299894</t>
+          <t>300220</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311452</t>
+          <t>311449</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>458227</t>
+          <t>458068</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>470404</t>
+          <t>470578</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>765128</t>
+          <t>765828</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>779679</t>
+          <t>780591</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9826</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13706</t>
+          <t>13885</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25213</t>
+          <t>24408</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17821</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32068</t>
+          <t>31916</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168916</t>
+          <t>168841</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175955</t>
+          <t>175876</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>183443</t>
+          <t>184248</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>194950</t>
+          <t>194771</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>355330</t>
+          <t>355482</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>369577</t>
+          <t>368809</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>4466</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12438</t>
+          <t>12818</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12796</t>
+          <t>12773</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24548</t>
+          <t>24418</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18915</t>
+          <t>18529</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32380</t>
+          <t>33654</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257198</t>
+          <t>256818</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265490</t>
+          <t>265170</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>232508</t>
+          <t>232638</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>244260</t>
+          <t>244283</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>494312</t>
+          <t>493038</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>507777</t>
+          <t>508163</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17491</t>
+          <t>17710</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37634</t>
+          <t>37380</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27721</t>
+          <t>25709</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82595</t>
+          <t>82658</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53851</t>
+          <t>52834</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108309</t>
+          <t>107222</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>586645</t>
+          <t>586899</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>606788</t>
+          <t>606569</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>766670</t>
+          <t>766607</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>821544</t>
+          <t>823556</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1365235</t>
+          <t>1366322</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1419693</t>
+          <t>1420710</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9021</t>
+          <t>8652</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20094</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8875</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23139</t>
+          <t>23600</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -13216,7 +13216,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>921575</t>
+          <t>921817</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>694757</t>
+          <t>694482</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>705830</t>
+          <t>706199</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1620433</t>
+          <t>1619972</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1634697</t>
+          <t>1634868</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>50926</t>
+          <t>51668</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>86019</t>
+          <t>87804</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>148904</t>
+          <t>149245</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>206724</t>
+          <t>208661</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>212144</t>
+          <t>215097</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>284391</t>
+          <t>282375</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3372311</t>
+          <t>3370526</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3407404</t>
+          <t>3406662</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3450978</t>
+          <t>3449041</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3508798</t>
+          <t>3508457</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6831641</t>
+          <t>6833657</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6903888</t>
+          <t>6900935</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A03-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A03-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>13272</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10581</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27232</t>
+          <t>28380</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16040</t>
+          <t>15620</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35692</t>
+          <t>36315</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>259850</t>
+          <t>259738</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270197</t>
+          <t>270383</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>233606</t>
+          <t>232458</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>250257</t>
+          <t>249607</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>498156</t>
+          <t>497533</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>517808</t>
+          <t>518228</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19724</t>
+          <t>19124</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13563</t>
+          <t>13718</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31710</t>
+          <t>32053</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20536</t>
+          <t>20418</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45538</t>
+          <t>44336</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>473351</t>
+          <t>473951</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>489229</t>
+          <t>489487</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>472239</t>
+          <t>471896</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>490386</t>
+          <t>490231</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>951486</t>
+          <t>952688</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>976488</t>
+          <t>976606</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>945</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11727</t>
+          <t>11343</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>11355</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26185</t>
+          <t>28099</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>13528</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33240</t>
+          <t>32823</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307119</t>
+          <t>307503</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317896</t>
+          <t>317901</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>309227</t>
+          <t>307313</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>324626</t>
+          <t>324057</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>621018</t>
+          <t>621435</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>640134</t>
+          <t>640730</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20190</t>
+          <t>18481</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17551</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37097</t>
+          <t>36610</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25865</t>
+          <t>27103</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50440</t>
+          <t>50185</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>338481</t>
+          <t>340190</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>352414</t>
+          <t>352715</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>334359</t>
+          <t>334846</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>353905</t>
+          <t>354790</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>679687</t>
+          <t>679942</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>704262</t>
+          <t>703024</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5572</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19298</t>
+          <t>19070</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19762</t>
+          <t>20572</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197831</t>
+          <t>197913</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188370</t>
+          <t>188598</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>202072</t>
+          <t>202096</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>391214</t>
+          <t>390404</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>405076</t>
+          <t>404983</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11868</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11434</t>
+          <t>10990</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27451</t>
+          <t>27305</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14848</t>
+          <t>14110</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33973</t>
+          <t>33086</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258943</t>
+          <t>260235</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268966</t>
+          <t>268975</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>250693</t>
+          <t>250839</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>266710</t>
+          <t>267154</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>514982</t>
+          <t>515869</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>534107</t>
+          <t>534845</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>10774</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29193</t>
+          <t>29636</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30087</t>
+          <t>30126</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55205</t>
+          <t>55741</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46097</t>
+          <t>45984</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76712</t>
+          <t>75710</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>585834</t>
+          <t>585391</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>603752</t>
+          <t>604253</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>583014</t>
+          <t>582478</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>608132</t>
+          <t>608093</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1176534</t>
+          <t>1177536</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1207149</t>
+          <t>1207262</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>11208</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28730</t>
+          <t>27936</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17741</t>
+          <t>17462</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37310</t>
+          <t>38280</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33384</t>
+          <t>32872</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60069</t>
+          <t>58221</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>714047</t>
+          <t>714841</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>731701</t>
+          <t>731569</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>746201</t>
+          <t>745231</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>765770</t>
+          <t>766049</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1466219</t>
+          <t>1468067</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1492904</t>
+          <t>1493416</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>57390</t>
+          <t>56909</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>91669</t>
+          <t>93723</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>154672</t>
+          <t>152853</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>206254</t>
+          <t>207030</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>222735</t>
+          <t>224272</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>286084</t>
+          <t>290756</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3183856</t>
+          <t>3181802</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3218135</t>
+          <t>3218616</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3172943</t>
+          <t>3172167</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3224525</t>
+          <t>3226344</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6368638</t>
+          <t>6363966</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6431987</t>
+          <t>6430450</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14714</t>
+          <t>14071</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9247</t>
+          <t>9285</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26380</t>
+          <t>27212</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14464</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35613</t>
+          <t>35375</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>275489</t>
+          <t>276132</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>287551</t>
+          <t>287565</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252949</t>
+          <t>252117</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>270082</t>
+          <t>270044</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>533919</t>
+          <t>534157</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>555068</t>
+          <t>554852</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20094</t>
+          <t>20481</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19873</t>
+          <t>20132</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42371</t>
+          <t>42784</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25936</t>
+          <t>26527</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54049</t>
+          <t>56616</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>485433</t>
+          <t>485046</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502376</t>
+          <t>502382</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>480360</t>
+          <t>479947</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502858</t>
+          <t>502599</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>974209</t>
+          <t>971642</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1002322</t>
+          <t>1001731</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10575</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12246</t>
+          <t>11793</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29834</t>
+          <t>29366</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16157</t>
+          <t>16011</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36018</t>
+          <t>35827</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312541</t>
+          <t>311589</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>321222</t>
+          <t>321221</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>310121</t>
+          <t>310589</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327709</t>
+          <t>328162</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>627053</t>
+          <t>627244</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>646914</t>
+          <t>647060</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12593</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23173</t>
+          <t>22506</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45398</t>
+          <t>46457</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27248</t>
+          <t>26235</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51201</t>
+          <t>51993</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>361389</t>
+          <t>362159</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>371930</t>
+          <t>371904</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>342576</t>
+          <t>341517</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>364801</t>
+          <t>365468</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>710755</t>
+          <t>709963</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>734708</t>
+          <t>735721</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11358</t>
+          <t>10332</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13295</t>
+          <t>13375</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31243</t>
+          <t>33329</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16413</t>
+          <t>14646</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37534</t>
+          <t>35994</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201260</t>
+          <t>202286</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211576</t>
+          <t>211588</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188348</t>
+          <t>186262</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206296</t>
+          <t>206216</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>394675</t>
+          <t>396215</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>415796</t>
+          <t>417563</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23335</t>
+          <t>23776</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9637</t>
+          <t>8990</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25457</t>
+          <t>24895</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>267924</t>
+          <t>267859</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>255805</t>
+          <t>255364</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271270</t>
+          <t>270947</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>527664</t>
+          <t>528226</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>543484</t>
+          <t>544131</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16792</t>
+          <t>16996</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33502</t>
+          <t>33127</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61044</t>
+          <t>60434</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39945</t>
+          <t>39601</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69386</t>
+          <t>69226</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>645996</t>
+          <t>645792</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>658906</t>
+          <t>659085</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>632809</t>
+          <t>633419</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>660351</t>
+          <t>660726</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1287255</t>
+          <t>1287415</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1316696</t>
+          <t>1317040</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14271</t>
+          <t>12591</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,82 +6472,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>35463</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>24193</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>48836</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>40961</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>29336</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>54533</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>1,84%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>35463</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>25978</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>49695</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>40961</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>29687</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>55725</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>762701</t>
+          <t>764381</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>774841</t>
+          <t>774806</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,82 +6585,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>98,38%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>723</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>786057</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>772684</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>797327</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>95,68%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>94,06%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>97,06%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1433</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1557531</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1543959</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>1569156</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>97,44%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>96,59%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>98,16%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>723</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>786057</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>771825</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>795542</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>95,68%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>93,95%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>96,84%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1433</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1557531</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1542767</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1568805</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>96,51%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>32689</t>
+          <t>31896</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>62370</t>
+          <t>62408</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>185266</t>
+          <t>184917</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>243139</t>
+          <t>244436</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>228931</t>
+          <t>227027</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>294050</t>
+          <t>293901</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3356818</t>
+          <t>3356780</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3386499</t>
+          <t>3387292</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3300955</t>
+          <t>3299658</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3358828</t>
+          <t>3359177</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6669232</t>
+          <t>6669381</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6734351</t>
+          <t>6736255</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>795</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9661</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12709</t>
+          <t>12561</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31380</t>
+          <t>31281</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15230</t>
+          <t>15313</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34787</t>
+          <t>36065</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>284100</t>
+          <t>284465</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292959</t>
+          <t>292966</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>257323</t>
+          <t>257422</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275994</t>
+          <t>276142</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>547677</t>
+          <t>546399</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>567234</t>
+          <t>567151</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12643</t>
+          <t>12569</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>5547</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19685</t>
+          <t>19317</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10358</t>
+          <t>10396</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27315</t>
+          <t>26902</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>489932</t>
+          <t>490006</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500390</t>
+          <t>500337</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>503399</t>
+          <t>503767</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>516882</t>
+          <t>517537</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>998344</t>
+          <t>998757</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1015301</t>
+          <t>1015263</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20560</t>
+          <t>20567</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22559</t>
+          <t>22582</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313753</t>
+          <t>313014</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>315749</t>
+          <t>315742</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>330420</t>
+          <t>330235</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>632315</t>
+          <t>632292</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>647689</t>
+          <t>648109</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11839</t>
+          <t>11417</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21111</t>
+          <t>19513</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42379</t>
+          <t>41801</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25028</t>
+          <t>25000</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49476</t>
+          <t>48651</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>358125</t>
+          <t>358547</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367963</t>
+          <t>368019</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>344904</t>
+          <t>345482</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366172</t>
+          <t>367770</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>707771</t>
+          <t>708596</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>732219</t>
+          <t>732247</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13277</t>
+          <t>13791</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3641</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15062</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>205891</t>
+          <t>205816</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>205310</t>
+          <t>204796</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215551</t>
+          <t>215764</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>414746</t>
+          <t>415269</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>426167</t>
+          <t>426084</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>783</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18585</t>
+          <t>17811</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>7219</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21709</t>
+          <t>21385</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254816</t>
+          <t>255573</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262333</t>
+          <t>262340</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>254530</t>
+          <t>255304</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>267776</t>
+          <t>268054</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>514529</t>
+          <t>514853</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>528872</t>
+          <t>529019</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9155</t>
+          <t>9511</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26200</t>
+          <t>26005</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17670</t>
+          <t>16524</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37897</t>
+          <t>36710</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31332</t>
+          <t>30275</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57259</t>
+          <t>57655</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>630358</t>
+          <t>630553</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>647403</t>
+          <t>647047</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>653397</t>
+          <t>654584</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>673624</t>
+          <t>674770</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1290593</t>
+          <t>1290197</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1316520</t>
+          <t>1317577</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13839</t>
+          <t>13561</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19336</t>
+          <t>19430</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42436</t>
+          <t>41268</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25764</t>
+          <t>26286</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51203</t>
+          <t>51403</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>764744</t>
+          <t>765022</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775609</t>
+          <t>775712</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>783731</t>
+          <t>784899</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>806831</t>
+          <t>806737</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1553547</t>
+          <t>1553347</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1578986</t>
+          <t>1578464</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>32914</t>
+          <t>32060</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>58279</t>
+          <t>56894</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>122626</t>
+          <t>123306</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>175335</t>
+          <t>171513</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>166431</t>
+          <t>165567</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>217995</t>
+          <t>219283</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3336071</t>
+          <t>3337456</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3361436</t>
+          <t>3362290</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3369207</t>
+          <t>3373029</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3421916</t>
+          <t>3421236</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6720897</t>
+          <t>6719609</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6772461</t>
+          <t>6773325</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -10697,27 +10697,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>9784</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23327</t>
+          <t>22728</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16655</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31519</t>
+          <t>30483</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>28134</t>
+          <t>27413</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20713</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37123</t>
+          <t>35959</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -10810,22 +10810,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>306636</t>
+          <t>314160</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>301884</t>
+          <t>309061</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309586</t>
+          <t>316720</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>266308</t>
+          <t>293333</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>258116</t>
+          <t>285578</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>272980</t>
+          <t>299600</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>572943</t>
+          <t>607493</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>563954</t>
+          <t>598947</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>580364</t>
+          <t>614977</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5450</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>12028</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13001</t>
+          <t>13948</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>8134</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19682</t>
+          <t>21024</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18452</t>
+          <t>19557</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12207</t>
+          <t>12879</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28116</t>
+          <t>28740</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>511943</t>
+          <t>524051</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>505048</t>
+          <t>517632</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>515292</t>
+          <t>527631</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>500724</t>
+          <t>531265</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>494043</t>
+          <t>524189</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>505561</t>
+          <t>537079</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1012666</t>
+          <t>1055316</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1003002</t>
+          <t>1046133</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1018911</t>
+          <t>1061994</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13476</t>
+          <t>12957</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21865</t>
+          <t>21484</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>27107</t>
+          <t>27481</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20298</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35278</t>
+          <t>36371</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>40582</t>
+          <t>40438</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30830</t>
+          <t>31042</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51715</t>
+          <t>51790</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>302084</t>
+          <t>302541</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>293695</t>
+          <t>294014</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>307457</t>
+          <t>307351</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>322021</t>
+          <t>328900</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>313850</t>
+          <t>320010</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328830</t>
+          <t>335858</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>624106</t>
+          <t>631442</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>612973</t>
+          <t>620090</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>633858</t>
+          <t>640838</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315560</t>
+          <t>315498</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315560</t>
+          <t>315498</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315560</t>
+          <t>315498</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664688</t>
+          <t>671880</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664688</t>
+          <t>671880</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664688</t>
+          <t>671880</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12337</t>
+          <t>11397</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9837</t>
+          <t>11815</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17319</t>
+          <t>19975</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>13687</t>
+          <t>15819</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7353</t>
+          <t>9658</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22116</t>
+          <t>26061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>308707</t>
+          <t>369141</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>300220</t>
+          <t>361748</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311449</t>
+          <t>371991</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>465550</t>
+          <t>409815</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>458068</t>
+          <t>401655</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>470578</t>
+          <t>414414</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>774257</t>
+          <t>778956</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>765828</t>
+          <t>768714</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>780591</t>
+          <t>785117</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>10970</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18556</t>
+          <t>18060</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13885</t>
+          <t>13332</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24408</t>
+          <t>23577</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>24113</t>
+          <t>23861</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>18196</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31916</t>
+          <t>30926</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>173185</t>
+          <t>199864</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168841</t>
+          <t>194695</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175876</t>
+          <t>202871</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>190100</t>
+          <t>209155</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>184248</t>
+          <t>203638</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>194771</t>
+          <t>213883</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>363285</t>
+          <t>409018</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>355482</t>
+          <t>401953</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>368809</t>
+          <t>414683</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7514</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4466</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12818</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17561</t>
+          <t>17557</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12773</t>
+          <t>12231</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24418</t>
+          <t>23733</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>25127</t>
+          <t>25071</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18529</t>
+          <t>19058</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33654</t>
+          <t>33518</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>262070</t>
+          <t>263193</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256818</t>
+          <t>257829</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265170</t>
+          <t>266309</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>239495</t>
+          <t>246193</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>232638</t>
+          <t>240017</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>244283</t>
+          <t>251519</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>501565</t>
+          <t>509386</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>493038</t>
+          <t>500939</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>508163</t>
+          <t>515399</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>26415</t>
+          <t>34611</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17710</t>
+          <t>23716</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37380</t>
+          <t>48291</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>58118</t>
+          <t>73210</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25709</t>
+          <t>59563</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82658</t>
+          <t>90776</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>84533</t>
+          <t>107821</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52834</t>
+          <t>90191</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>107222</t>
+          <t>131346</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>597864</t>
+          <t>685076</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>586899</t>
+          <t>671396</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>606569</t>
+          <t>695971</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>791147</t>
+          <t>698847</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>766607</t>
+          <t>681281</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>823556</t>
+          <t>712494</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1389011</t>
+          <t>1383923</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1366322</t>
+          <t>1360398</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1420710</t>
+          <t>1401553</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6903</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,22 +13133,22 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>13663</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>10013</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20369</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>15417</t>
+          <t>17195</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23600</t>
+          <t>24749</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -13211,27 +13211,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>926966</t>
+          <t>796212</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>921817</t>
+          <t>792025</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13246,27 +13246,27 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>701188</t>
+          <t>814671</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>694482</t>
+          <t>807984</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>706199</t>
+          <t>819993</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1628155</t>
+          <t>1610883</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1619972</t>
+          <t>1603329</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1634868</t>
+          <t>1617049</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>68876</t>
+          <t>77041</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>51668</t>
+          <t>60192</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>87804</t>
+          <t>93936</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>181169</t>
+          <t>200134</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>149245</t>
+          <t>178432</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>208661</t>
+          <t>226139</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>250045</t>
+          <t>277175</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>215097</t>
+          <t>249208</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>282375</t>
+          <t>307629</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3389454</t>
+          <t>3454239</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3370526</t>
+          <t>3437344</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3406662</t>
+          <t>3471088</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3476533</t>
+          <t>3532179</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3449041</t>
+          <t>3506174</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3508457</t>
+          <t>3553881</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6865987</t>
+          <t>6986418</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6833657</t>
+          <t>6955964</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6900935</t>
+          <t>7014385</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
